--- a/backtest_runs/20260410_193731/by_symbol/RUPL/RUPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/RUPL/RUPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>112250.03</v>
@@ -817,7 +817,7 @@
         <v>-7362.549999999993</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>104887.48</v>
@@ -1047,7 +1047,7 @@
         <v>-908.5700000000085</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>119236.62</v>
@@ -1139,7 +1139,7 @@
         <v>-814.5799999999938</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>118422.04</v>
@@ -1185,7 +1185,7 @@
         <v>-8177.129999999998</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>110244.91</v>
@@ -1323,7 +1323,7 @@
         <v>-7801.170000000006</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>110965.5</v>
@@ -1415,7 +1415,7 @@
         <v>-1159.210000000003</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>111404.12</v>
